--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36848-2026 artfynd.xlsx
+++ b/artfynd/A 36848-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481205</v>
       </c>
       <c r="B2" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
